--- a/MegaProject/Driver_Monitoring_system/driver_monitoring_system.xlsx
+++ b/MegaProject/Driver_Monitoring_system/driver_monitoring_system.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ia97974\Desktop\51856\EE_PythonBatch1\MegaProject\Driver_Monitoring_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3555490-8380-4137-96D8-CD76949D69C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{607FBB95-44F7-4913-86F9-90631FB6A3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="330">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1019,9 +1019,6 @@
     <t>Attention Score / Level</t>
   </si>
   <si>
-    <t>Derived from Eye Closure %, Blink Rate, and Head Pose</t>
-  </si>
-  <si>
     <t>Represents overall driver attentiveness. Higher scores indicate better focus and alertness.</t>
   </si>
   <si>
@@ -1062,6 +1059,48 @@
   </si>
   <si>
     <t>Critical values detected in eye closure, blink rate, or attention score. Immediate attention is recommended.</t>
+  </si>
+  <si>
+    <t>Attention Score=(0.60×Eye Score)+(0.25×Blink Score)+(0.15×Head Score)</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Eye Closure Score</t>
+  </si>
+  <si>
+    <t>Blink Score</t>
+  </si>
+  <si>
+    <t>Head Pitch Score</t>
+  </si>
+  <si>
+    <t>Weight Distribution</t>
+  </si>
+  <si>
+    <t>Eye Closure Score=100−Eye Closure Percentage</t>
+  </si>
+  <si>
+    <t>Head Pitch Score=100−(Head Pitch Angle×4)</t>
+  </si>
+  <si>
+    <t>Blink Score=100−((15−Blink Rate)×5)</t>
+  </si>
+  <si>
+    <t>Head Pitch Score Formula</t>
+  </si>
+  <si>
+    <t>Blink Rate Score Formula</t>
+  </si>
+  <si>
+    <t>Eye Closure Score Formula</t>
+  </si>
+  <si>
+    <t>Parameter used in Python coding</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1146,6 +1185,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7858,11 +7904,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E69827B-8C65-4655-86E1-BF6CB6A862BC}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.140625" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="2" max="2" width="65.140625" customWidth="1"/>
     <col min="3" max="3" width="52.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7977,89 +8023,161 @@
         <v>300</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>303</v>
-      </c>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
+      <c r="A13" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
+      <c r="A14" s="12" t="s">
+        <v>301</v>
+      </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="B15" s="8"/>
+      <c r="A15" s="11" t="s">
+        <v>322</v>
+      </c>
       <c r="C15" s="8"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C16" s="8"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="10">
+        <v>0.6</v>
+      </c>
+      <c r="C17" s="8"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B18" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="C18" s="8"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="C19" s="8"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="8"/>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="B30" s="8"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B16" s="3" t="s">
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C16" s="8"/>
-    </row>
-    <row r="17" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+      <c r="B32" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B17" s="6" t="s">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="B33" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B18" s="6" t="s">
+    </row>
+    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+      <c r="B34" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B19" s="6" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="B35" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B20" s="6" t="s">
+    </row>
+    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="B36" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/MegaProject/Driver_Monitoring_system/driver_monitoring_system.xlsx
+++ b/MegaProject/Driver_Monitoring_system/driver_monitoring_system.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ia97974\Desktop\51856\EE_PythonBatch1\MegaProject\Driver_Monitoring_system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{607FBB95-44F7-4913-86F9-90631FB6A3B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E373FD6-48FC-4A89-BCBA-0F8181F0BDD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="3270" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="331">
   <si>
     <t>Timestamp</t>
   </si>
@@ -1101,6 +1101,9 @@
   </si>
   <si>
     <t>Parameter used in Python coding</t>
+  </si>
+  <si>
+    <t>https://pmc.ncbi.nlm.nih.gov/articles/PMC10108649/?</t>
   </si>
 </sst>
 </file>
@@ -1551,13 +1554,13 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3111,13 +3114,13 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4671,13 +4674,13 @@
         <v>0</v>
       </c>
       <c r="F122">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G122">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -6257,13 +6260,13 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
@@ -8064,7 +8067,9 @@
       <c r="B17" s="10">
         <v>0.6</v>
       </c>
-      <c r="C17" s="8"/>
+      <c r="C17" s="8" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
